--- a/12628961.xlsx
+++ b/12628961.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E08C1F9F-B0E4-41DA-B2A8-8A1F030F1E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFA467F8-9883-42D7-B222-CD27661D6B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -211,6 +211,18 @@
   </si>
   <si>
     <t xml:space="preserve">Too many Breaks </t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -991,7 +1003,7 @@
     </row>
     <row r="6" spans="1:14" ht="14.25">
       <c r="A6" s="8">
-        <v>46224</v>
+        <v>46286</v>
       </c>
       <c r="B6">
         <v>380</v>
@@ -1036,47 +1048,91 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="15">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B7">
+        <v>350</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7">
+        <v>350</v>
+      </c>
+      <c r="G7" s="14">
+        <v>7</v>
+      </c>
+      <c r="H7">
+        <v>210</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" ref="J6:J69" si="1">IF(I7="","",1440-I7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="15">
+      <c r="A8" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B8">
+        <v>500</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>50</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>300</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>60</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14">
